--- a/raw_data/edc_ex.xlsx
+++ b/raw_data/edc_ex.xlsx
@@ -10,33 +10,90 @@
     <sheet name="edc_ex" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="edc_ex">'edc_ex'!$A$1:$D$6</definedName>
+    <definedName name="edc_ex">'edc_ex'!$A$1:$M$8</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>SUBJID</t>
   </si>
   <si>
+    <t>VISIT</t>
+  </si>
+  <si>
+    <t>TRT</t>
+  </si>
+  <si>
+    <t>DOSE</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
     <t>STDT</t>
   </si>
   <si>
     <t>ENDT</t>
   </si>
   <si>
-    <t>DOSE</t>
+    <t>LOT</t>
+  </si>
+  <si>
+    <t>ROUTE</t>
+  </si>
+  <si>
+    <t>FREQ</t>
+  </si>
+  <si>
+    <t>FORM</t>
+  </si>
+  <si>
+    <t>ADJ</t>
+  </si>
+  <si>
+    <t>ADJRS</t>
   </si>
   <si>
     <t>101</t>
   </si>
   <si>
+    <t>CYCLE_1</t>
+  </si>
+  <si>
+    <t>DRUG_A</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
     <t>15-JAN-2026</t>
   </si>
   <si>
+    <t>LOT-A1</t>
+  </si>
+  <si>
+    <t>INTRAVENOUS</t>
+  </si>
+  <si>
+    <t>Q3W</t>
+  </si>
+  <si>
+    <t>SOLUTION_FOR_INJECTION</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>CYCLE_2</t>
+  </si>
+  <si>
     <t>05-FEB-2026</t>
   </si>
   <si>
@@ -46,7 +103,34 @@
     <t>20-JAN-2026</t>
   </si>
   <si>
+    <t>LOT-A2</t>
+  </si>
+  <si>
+    <t>10-FEB-2026</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>ADVERSE_EVENT</t>
+  </si>
+  <si>
     <t>103</t>
+  </si>
+  <si>
+    <t>PLACEBO</t>
+  </si>
+  <si>
+    <t>LOT-P1</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>DOSE_MISSED</t>
   </si>
   <si>
     <t>105</t>
@@ -410,12 +494,21 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="31" customWidth="1"/>
+    <col min="12" max="12" width="4" customWidth="1"/>
+    <col min="13" max="13" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -428,75 +521,316 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>2.e+002</v>
       </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>2.e+002</v>
       </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>2.e+002</v>
       </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D5">
+        <v>1.e+002</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6">
         <v>0.e+000</v>
       </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
         <v>2.e+002</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
